--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2005E197-8424-4502-A1B0-03173C263EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6F7C1EF-CB2F-4976-B0B8-89AFC1290E6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -17518,7 +17518,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>180826</v>
+        <v>90920263</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18347,7 +18347,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
@@ -18398,7 +18398,7 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AC2" s="19">
         <v>150</v>
